--- a/JsonConverter/ExcelFiles/OO_Ingredient.xlsx
+++ b/JsonConverter/ExcelFiles/OO_Ingredient.xlsx
@@ -1,141 +1,87 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="12770" yWindow="2240" windowWidth="19820" windowHeight="18420"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="12770" yWindow="2240" windowWidth="19820" windowHeight="18420" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DNTable_Ingredient" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="zgynNiv2YVTupuAxVwKvj3LXvSi69gCaqo2XUeu/LZo="/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
-  <si>
-    <t>캐릭터 고유 ID</t>
-  </si>
-  <si>
-    <t>캐릭터 전체 컨셉이나 스토리</t>
-  </si>
-  <si>
-    <t>(name)</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>Id</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>스킬</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillList</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>캐릭터 별로 무기가 고정인 경우용</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>UseWeaponId</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>BasicCostumeId</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="9">
     <font>
+      <name val="Arial"/>
+      <color rgb="FF000000"/>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="&quot;맑은 고딕&quot;"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <color rgb="FF000000"/>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="&quot;맑은 고딕&quot;"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="10"/>
     </font>
     <font>
+      <name val="&quot;맑은 고딕&quot;"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <color rgb="FF008000"/>
       <sz val="11"/>
-      <color rgb="FF008000"/>
-      <name val="&quot;맑은 고딕&quot;"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
     </font>
     <font>
+      <name val="Arial"/>
+      <charset val="129"/>
+      <family val="3"/>
       <sz val="8"/>
-      <name val="Arial"/>
-      <family val="3"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <color rgb="FF000000"/>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
+      <name val="Arial"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <color rgb="FF000000"/>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="3"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="8">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -166,13 +112,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
+        <fgColor theme="7" tint="0.7999816888943144"/>
         <bgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
+        <fgColor theme="7" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -219,50 +165,110 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="18">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -463,400 +469,496 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1000"/>
-  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
+  <dimension ref="A1:O35"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="19.453125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="19.54296875" style="3" customWidth="1"/>
-    <col min="3" max="3" width="50.7265625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="20.26953125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="30.54296875" style="3" customWidth="1"/>
-    <col min="6" max="6" width="26.54296875" style="3" customWidth="1"/>
-    <col min="7" max="16384" width="12.54296875" style="3"/>
+    <col width="20" customWidth="1" style="3" min="1" max="1"/>
+    <col width="16" customWidth="1" style="3" min="2" max="2"/>
+    <col width="80" customWidth="1" style="3" min="3" max="3"/>
+    <col width="28" customWidth="1" style="3" min="4" max="4"/>
+    <col width="14" customWidth="1" style="3" min="5" max="5"/>
+    <col width="16" customWidth="1" style="3" min="6" max="6"/>
+    <col width="12.54296875" customWidth="1" style="3" min="7" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" ht="13">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" s="13" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A3" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
-    </row>
-    <row r="5" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A5" s="4"/>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
-    </row>
-    <row r="6" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A6" s="6"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="5"/>
-      <c r="O6" s="5"/>
-    </row>
-    <row r="7" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
-      <c r="M7" s="5"/>
-      <c r="N7" s="5"/>
-      <c r="O7" s="5"/>
-    </row>
-    <row r="8" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
-      <c r="M8" s="5"/>
-      <c r="N8" s="5"/>
-      <c r="O8" s="5"/>
-    </row>
-    <row r="9" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5"/>
-      <c r="M9" s="5"/>
-      <c r="N9" s="5"/>
-      <c r="O9" s="5"/>
-    </row>
-    <row r="10" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
-      <c r="L10" s="5"/>
-      <c r="M10" s="5"/>
-      <c r="N10" s="5"/>
-      <c r="O10" s="5"/>
-    </row>
-    <row r="11" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5"/>
-      <c r="L11" s="5"/>
-      <c r="M11" s="5"/>
-      <c r="N11" s="5"/>
-      <c r="O11" s="5"/>
-    </row>
-    <row r="12" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5"/>
-      <c r="L12" s="5"/>
-      <c r="M12" s="5"/>
-      <c r="N12" s="5"/>
-      <c r="O12" s="5"/>
-    </row>
-    <row r="13" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
-      <c r="L13" s="5"/>
-      <c r="M13" s="5"/>
-      <c r="N13" s="5"/>
-      <c r="O13" s="5"/>
-    </row>
-    <row r="14" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
-      <c r="L14" s="5"/>
-      <c r="M14" s="5"/>
-      <c r="N14" s="5"/>
-      <c r="O14" s="5"/>
-    </row>
-    <row r="15" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5"/>
-      <c r="L15" s="5"/>
-      <c r="M15" s="5"/>
-      <c r="N15" s="5"/>
-      <c r="O15" s="5"/>
-    </row>
-    <row r="16" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-    </row>
-    <row r="17" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-    </row>
-    <row r="18" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-    </row>
-    <row r="19" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-    </row>
-    <row r="20" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-    </row>
-    <row r="21" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A21" s="9"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-    </row>
-    <row r="22" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A22" s="9"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-    </row>
-    <row r="23" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A23" s="9"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-    </row>
-    <row r="24" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A24" s="9"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-    </row>
-    <row r="25" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A25" s="9"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="E25" s="5"/>
-    </row>
-    <row r="26" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A26" s="10"/>
-      <c r="B26" s="10"/>
-      <c r="C26" s="10"/>
-      <c r="E26" s="5"/>
-    </row>
-    <row r="27" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A27" s="10"/>
-      <c r="B27" s="10"/>
-      <c r="C27" s="10"/>
-      <c r="E27" s="5"/>
-    </row>
-    <row r="28" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A28" s="10"/>
-      <c r="B28" s="10"/>
-      <c r="C28" s="10"/>
-      <c r="E28" s="5"/>
-    </row>
-    <row r="29" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A29" s="10"/>
-      <c r="B29" s="10"/>
-      <c r="C29" s="10"/>
-    </row>
-    <row r="30" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A30" s="10"/>
-      <c r="B30" s="10"/>
-      <c r="C30" s="10"/>
-    </row>
-    <row r="31" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A31" s="10"/>
-      <c r="B31" s="10"/>
-      <c r="C31" s="10"/>
-    </row>
-    <row r="32" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A32" s="11"/>
-      <c r="B32" s="11"/>
-      <c r="C32" s="11"/>
-    </row>
-    <row r="33" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A33" s="11"/>
-      <c r="B33" s="11"/>
-      <c r="C33" s="11"/>
-    </row>
-    <row r="34" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A34" s="11"/>
-      <c r="B34" s="11"/>
-      <c r="C34" s="11"/>
-    </row>
-    <row r="35" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A35" s="11"/>
-      <c r="B35" s="11"/>
-      <c r="C35" s="11"/>
-    </row>
-    <row r="36" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="37" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="38" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="39" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="40" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="41" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="42" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="43" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="44" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="45" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="46" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="47" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="48" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="1" ht="15.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>재료 고유 ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>재료 이름</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>재료 설명</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>아이콘 리소스 경로</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>재료 등급</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>최대 중첩 수</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="13" customHeight="1">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15.75" customFormat="1" customHeight="1" s="13">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="inlineStr">
+        <is>
+          <t>IconPath</t>
+        </is>
+      </c>
+      <c r="E3" s="14" t="inlineStr">
+        <is>
+          <t>Grade</t>
+        </is>
+      </c>
+      <c r="F3" s="15" t="inlineStr">
+        <is>
+          <t>MaxStackCount</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15.75" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Ing_Rice_01</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>쌀</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>춘향의 아버님이 내어주신 기름진 쌀. 모란의 기계 솥을 거치면 백성들의 허기를 단숨에 채워줄 따스한 밥과 떡이 된다.</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr"/>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="F4" s="16" t="n">
+        <v>99</v>
+      </c>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
+      <c r="I4" s="5" t="n"/>
+      <c r="J4" s="5" t="n"/>
+      <c r="K4" s="5" t="n"/>
+      <c r="L4" s="5" t="n"/>
+      <c r="M4" s="5" t="n"/>
+      <c r="N4" s="5" t="n"/>
+      <c r="O4" s="5" t="n"/>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="17" t="inlineStr">
+        <is>
+          <t>Ing_Pumpkin_01</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>호박</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>굶주린 동쪽 마을 마당구석에서 자라난 호박. 쌀과 함께 푹 고아내면 얼어붙은 몸을 녹이는 달콤한 호박죽이 완성된다.</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr"/>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>99</v>
+      </c>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="15.75" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Ing_Veggie_01</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>채소</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>모란의 집 텃밭에서 정성껏 기른 소박한 채소 바구니. 비록 재익 군이 다른 음식을 다 먹어치우는 바람에 이것만 남았지만, 갓 따낸 싱그러운 생기가 가득하다.</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>99</v>
+      </c>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="n"/>
+      <c r="N6" s="5" t="n"/>
+      <c r="O6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="15.75" customHeight="1">
+      <c r="A7" s="4" t="n"/>
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n"/>
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="5" t="n"/>
+      <c r="K7" s="5" t="n"/>
+      <c r="L7" s="5" t="n"/>
+      <c r="M7" s="5" t="n"/>
+      <c r="N7" s="5" t="n"/>
+      <c r="O7" s="5" t="n"/>
+    </row>
+    <row r="8" ht="15.75" customHeight="1">
+      <c r="A8" s="7" t="n"/>
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="7" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="5" t="n"/>
+      <c r="K8" s="5" t="n"/>
+      <c r="L8" s="5" t="n"/>
+      <c r="M8" s="5" t="n"/>
+      <c r="N8" s="5" t="n"/>
+      <c r="O8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="15.75" customHeight="1">
+      <c r="A9" s="7" t="n"/>
+      <c r="B9" s="7" t="n"/>
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="5" t="n"/>
+      <c r="J9" s="5" t="n"/>
+      <c r="K9" s="5" t="n"/>
+      <c r="L9" s="5" t="n"/>
+      <c r="M9" s="5" t="n"/>
+      <c r="N9" s="5" t="n"/>
+      <c r="O9" s="5" t="n"/>
+    </row>
+    <row r="10" ht="15.75" customHeight="1">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="1" t="n"/>
+      <c r="C10" s="1" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n"/>
+      <c r="I10" s="5" t="n"/>
+      <c r="J10" s="5" t="n"/>
+      <c r="K10" s="5" t="n"/>
+      <c r="L10" s="5" t="n"/>
+      <c r="M10" s="5" t="n"/>
+      <c r="N10" s="5" t="n"/>
+      <c r="O10" s="5" t="n"/>
+    </row>
+    <row r="11" ht="15.75" customHeight="1">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="1" t="n"/>
+      <c r="C11" s="1" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="n"/>
+      <c r="I11" s="5" t="n"/>
+      <c r="J11" s="5" t="n"/>
+      <c r="K11" s="5" t="n"/>
+      <c r="L11" s="5" t="n"/>
+      <c r="M11" s="5" t="n"/>
+      <c r="N11" s="5" t="n"/>
+      <c r="O11" s="5" t="n"/>
+    </row>
+    <row r="12" ht="15.75" customHeight="1">
+      <c r="A12" s="7" t="n"/>
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="7" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n"/>
+      <c r="I12" s="5" t="n"/>
+      <c r="J12" s="5" t="n"/>
+      <c r="K12" s="5" t="n"/>
+      <c r="L12" s="5" t="n"/>
+      <c r="M12" s="5" t="n"/>
+      <c r="N12" s="5" t="n"/>
+      <c r="O12" s="5" t="n"/>
+    </row>
+    <row r="13" ht="15.75" customHeight="1">
+      <c r="A13" s="4" t="n"/>
+      <c r="B13" s="4" t="n"/>
+      <c r="C13" s="4" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="5" t="n"/>
+      <c r="I13" s="5" t="n"/>
+      <c r="J13" s="5" t="n"/>
+      <c r="K13" s="5" t="n"/>
+      <c r="L13" s="5" t="n"/>
+      <c r="M13" s="5" t="n"/>
+      <c r="N13" s="5" t="n"/>
+      <c r="O13" s="5" t="n"/>
+    </row>
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="1" t="n"/>
+      <c r="C14" s="1" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n"/>
+      <c r="I14" s="5" t="n"/>
+      <c r="J14" s="5" t="n"/>
+      <c r="K14" s="5" t="n"/>
+      <c r="L14" s="5" t="n"/>
+      <c r="M14" s="5" t="n"/>
+      <c r="N14" s="5" t="n"/>
+      <c r="O14" s="5" t="n"/>
+    </row>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="1" t="n"/>
+      <c r="C15" s="1" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="n"/>
+      <c r="I15" s="5" t="n"/>
+      <c r="J15" s="5" t="n"/>
+      <c r="K15" s="5" t="n"/>
+      <c r="L15" s="5" t="n"/>
+      <c r="M15" s="5" t="n"/>
+      <c r="N15" s="5" t="n"/>
+      <c r="O15" s="5" t="n"/>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="8" t="n"/>
+      <c r="B16" s="8" t="n"/>
+      <c r="C16" s="8" t="n"/>
+    </row>
+    <row r="17" ht="15.75" customHeight="1">
+      <c r="A17" s="9" t="n"/>
+      <c r="B17" s="9" t="n"/>
+      <c r="C17" s="9" t="n"/>
+    </row>
+    <row r="18" ht="15.75" customHeight="1">
+      <c r="A18" s="9" t="n"/>
+      <c r="B18" s="9" t="n"/>
+      <c r="C18" s="9" t="n"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1">
+      <c r="A19" s="9" t="n"/>
+      <c r="B19" s="9" t="n"/>
+      <c r="C19" s="9" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+    </row>
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="A20" s="9" t="n"/>
+      <c r="B20" s="9" t="n"/>
+      <c r="C20" s="9" t="n"/>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="9" t="n"/>
+      <c r="B21" s="9" t="n"/>
+      <c r="C21" s="9" t="n"/>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="9" t="n"/>
+      <c r="B22" s="9" t="n"/>
+      <c r="C22" s="9" t="n"/>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="9" t="n"/>
+      <c r="B23" s="9" t="n"/>
+      <c r="C23" s="9" t="n"/>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="9" t="n"/>
+      <c r="B24" s="9" t="n"/>
+      <c r="C24" s="9" t="n"/>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="9" t="n"/>
+      <c r="B25" s="9" t="n"/>
+      <c r="C25" s="9" t="n"/>
+      <c r="E25" s="5" t="n"/>
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="10" t="n"/>
+      <c r="B26" s="10" t="n"/>
+      <c r="C26" s="10" t="n"/>
+      <c r="E26" s="5" t="n"/>
+    </row>
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="10" t="n"/>
+      <c r="B27" s="10" t="n"/>
+      <c r="C27" s="10" t="n"/>
+      <c r="E27" s="5" t="n"/>
+    </row>
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="10" t="n"/>
+      <c r="B28" s="10" t="n"/>
+      <c r="C28" s="10" t="n"/>
+      <c r="E28" s="5" t="n"/>
+    </row>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="10" t="n"/>
+      <c r="B29" s="10" t="n"/>
+      <c r="C29" s="10" t="n"/>
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="10" t="n"/>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+    </row>
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="10" t="n"/>
+      <c r="B31" s="10" t="n"/>
+      <c r="C31" s="10" t="n"/>
+    </row>
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="11" t="n"/>
+      <c r="B32" s="11" t="n"/>
+      <c r="C32" s="11" t="n"/>
+    </row>
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="A33" s="11" t="n"/>
+      <c r="B33" s="11" t="n"/>
+      <c r="C33" s="11" t="n"/>
+    </row>
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="A34" s="11" t="n"/>
+      <c r="B34" s="11" t="n"/>
+      <c r="C34" s="11" t="n"/>
+    </row>
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="A35" s="11" t="n"/>
+      <c r="B35" s="11" t="n"/>
+      <c r="C35" s="11" t="n"/>
+    </row>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="15.75" customHeight="1"/>
+    <row r="38" ht="15.75" customHeight="1"/>
+    <row r="39" ht="15.75" customHeight="1"/>
+    <row r="40" ht="15.75" customHeight="1"/>
+    <row r="41" ht="15.75" customHeight="1"/>
+    <row r="42" ht="15.75" customHeight="1"/>
+    <row r="43" ht="15.75" customHeight="1"/>
+    <row r="44" ht="15.75" customHeight="1"/>
+    <row r="45" ht="15.75" customHeight="1"/>
+    <row r="46" ht="15.75" customHeight="1"/>
+    <row r="47" ht="15.75" customHeight="1"/>
+    <row r="48" ht="15.75" customHeight="1"/>
     <row r="49" ht="15.75" customHeight="1"/>
     <row r="50" ht="15.75" customHeight="1"/>
     <row r="51" ht="15.75" customHeight="1"/>
@@ -1810,8 +1912,7 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/OO_Ingredient.xlsx
+++ b/JsonConverter/ExcelFiles/OO_Ingredient.xlsx
@@ -1,87 +1,169 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="12770" yWindow="2240" windowWidth="19820" windowHeight="18420" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="12770" yWindow="2240" windowWidth="19820" windowHeight="18420"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DNTable_Ingredient" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="DNTable_Ingredient" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="25">
+  <si>
+    <t>재료 고유 ID</t>
+  </si>
+  <si>
+    <t>재료 이름</t>
+  </si>
+  <si>
+    <t>재료 설명</t>
+  </si>
+  <si>
+    <t>아이콘 리소스 경로</t>
+  </si>
+  <si>
+    <t>재료 등급</t>
+  </si>
+  <si>
+    <t>최대 중첩 수</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>Id</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>IconPath</t>
+  </si>
+  <si>
+    <t>Grade</t>
+  </si>
+  <si>
+    <t>MaxStackCount</t>
+  </si>
+  <si>
+    <t>쌀</t>
+  </si>
+  <si>
+    <t>춘향의 아버님이 내어주신 기름진 쌀. 모란의 기계 솥을 거치면 백성들의 허기를 단숨에 채워줄 따스한 밥과 떡이 된다.</t>
+  </si>
+  <si>
+    <t>일반</t>
+  </si>
+  <si>
+    <t>Ing_Pumpkin_01</t>
+  </si>
+  <si>
+    <t>호박</t>
+  </si>
+  <si>
+    <t>굶주린 동쪽 마을 마당구석에서 자라난 호박. 쌀과 함께 푹 고아내면 얼어붙은 몸을 녹이는 달콤한 호박죽이 완성된다.</t>
+  </si>
+  <si>
+    <t>채소</t>
+  </si>
+  <si>
+    <t>모란의 집 텃밭에서 정성껏 기른 소박한 채소 바구니. 비록 재익 군이 다른 음식을 다 먹어치우는 바람에 이것만 남았지만, 갓 따낸 싱그러운 생기가 가득하다.</t>
+  </si>
+  <si>
+    <t>조기</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ing_Veggie_01</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ing_Rice_01</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="9">
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="&quot;맑은 고딕&quot;"/>
+      <family val="3"/>
       <charset val="129"/>
-      <family val="3"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="10"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF008000"/>
       <name val="&quot;맑은 고딕&quot;"/>
+      <family val="3"/>
       <charset val="129"/>
-      <family val="3"/>
-      <color rgb="FF008000"/>
-      <sz val="11"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
     </font>
     <font>
+      <sz val="8"/>
       <name val="Arial"/>
+      <family val="3"/>
       <charset val="129"/>
-      <family val="3"/>
-      <sz val="8"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="맑은 고딕"/>
+      <family val="3"/>
       <charset val="129"/>
-      <family val="3"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="3"/>
       <charset val="129"/>
-      <family val="3"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="8">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -112,13 +194,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.7999816888943144"/>
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.7999816888943144"/>
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -166,109 +248,47 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="18">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -469,496 +489,438 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
-    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O35"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
+  <dimension ref="A1:O1000"/>
+  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="20" customWidth="1" style="3" min="1" max="1"/>
-    <col width="16" customWidth="1" style="3" min="2" max="2"/>
-    <col width="80" customWidth="1" style="3" min="3" max="3"/>
-    <col width="28" customWidth="1" style="3" min="4" max="4"/>
-    <col width="14" customWidth="1" style="3" min="5" max="5"/>
-    <col width="16" customWidth="1" style="3" min="6" max="6"/>
-    <col width="12.54296875" customWidth="1" style="3" min="7" max="16384"/>
+    <col min="1" max="1" width="20" style="3" customWidth="1"/>
+    <col min="2" max="2" width="16" style="3" customWidth="1"/>
+    <col min="3" max="3" width="80" style="3" customWidth="1"/>
+    <col min="4" max="4" width="28" style="3" customWidth="1"/>
+    <col min="5" max="5" width="14" style="3" customWidth="1"/>
+    <col min="6" max="6" width="16" style="3" customWidth="1"/>
+    <col min="7" max="7" width="12.54296875" style="3" customWidth="1"/>
+    <col min="8" max="16384" width="12.54296875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>재료 고유 ID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>재료 이름</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>재료 설명</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>아이콘 리소스 경로</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>재료 등급</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>최대 중첩 수</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="13" customHeight="1">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="15.75" customFormat="1" customHeight="1" s="13">
-      <c r="A3" s="12" t="inlineStr">
-        <is>
-          <t>Id</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C3" s="12" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>IconPath</t>
-        </is>
-      </c>
-      <c r="E3" s="14" t="inlineStr">
-        <is>
-          <t>Grade</t>
-        </is>
-      </c>
-      <c r="F3" s="15" t="inlineStr">
-        <is>
-          <t>MaxStackCount</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Ing_Rice_01</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>쌀</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>춘향의 아버님이 내어주신 기름진 쌀. 모란의 기계 솥을 거치면 백성들의 허기를 단숨에 채워줄 따스한 밥과 떡이 된다.</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>일반</t>
-        </is>
-      </c>
-      <c r="F4" s="16" t="n">
+    <row r="1" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="13" customHeight="1">
+      <c r="A2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" s="13" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A3" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="16">
         <v>99</v>
       </c>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="5" t="n"/>
-      <c r="I4" s="5" t="n"/>
-      <c r="J4" s="5" t="n"/>
-      <c r="K4" s="5" t="n"/>
-      <c r="L4" s="5" t="n"/>
-      <c r="M4" s="5" t="n"/>
-      <c r="N4" s="5" t="n"/>
-      <c r="O4" s="5" t="n"/>
-    </row>
-    <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="17" t="inlineStr">
-        <is>
-          <t>Ing_Pumpkin_01</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>호박</t>
-        </is>
-      </c>
-      <c r="C5" s="17" t="inlineStr">
-        <is>
-          <t>굶주린 동쪽 마을 마당구석에서 자라난 호박. 쌀과 함께 푹 고아내면 얼어붙은 몸을 녹이는 달콤한 호박죽이 완성된다.</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>일반</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="n">
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
+    </row>
+    <row r="5" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A5" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="5">
         <v>99</v>
       </c>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="5" t="n"/>
-      <c r="I5" s="5" t="n"/>
-      <c r="J5" s="5" t="n"/>
-      <c r="K5" s="5" t="n"/>
-      <c r="L5" s="5" t="n"/>
-      <c r="M5" s="5" t="n"/>
-      <c r="N5" s="5" t="n"/>
-      <c r="O5" s="5" t="n"/>
-    </row>
-    <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Ing_Veggie_01</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>채소</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>모란의 집 텃밭에서 정성껏 기른 소박한 채소 바구니. 비록 재익 군이 다른 음식을 다 먹어치우는 바람에 이것만 남았지만, 갓 따낸 싱그러운 생기가 가득하다.</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>일반</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="n">
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
+    </row>
+    <row r="6" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A6" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" s="5">
         <v>99</v>
       </c>
-      <c r="G6" s="5" t="n"/>
-      <c r="H6" s="5" t="n"/>
-      <c r="I6" s="5" t="n"/>
-      <c r="J6" s="5" t="n"/>
-      <c r="K6" s="5" t="n"/>
-      <c r="L6" s="5" t="n"/>
-      <c r="M6" s="5" t="n"/>
-      <c r="N6" s="5" t="n"/>
-      <c r="O6" s="5" t="n"/>
-    </row>
-    <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="4" t="n"/>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="5" t="n"/>
-      <c r="H7" s="5" t="n"/>
-      <c r="I7" s="5" t="n"/>
-      <c r="J7" s="5" t="n"/>
-      <c r="K7" s="5" t="n"/>
-      <c r="L7" s="5" t="n"/>
-      <c r="M7" s="5" t="n"/>
-      <c r="N7" s="5" t="n"/>
-      <c r="O7" s="5" t="n"/>
-    </row>
-    <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="7" t="n"/>
-      <c r="B8" s="7" t="n"/>
-      <c r="C8" s="7" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n"/>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="5" t="n"/>
-      <c r="K8" s="5" t="n"/>
-      <c r="L8" s="5" t="n"/>
-      <c r="M8" s="5" t="n"/>
-      <c r="N8" s="5" t="n"/>
-      <c r="O8" s="5" t="n"/>
-    </row>
-    <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="7" t="n"/>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="5" t="n"/>
-      <c r="I9" s="5" t="n"/>
-      <c r="J9" s="5" t="n"/>
-      <c r="K9" s="5" t="n"/>
-      <c r="L9" s="5" t="n"/>
-      <c r="M9" s="5" t="n"/>
-      <c r="N9" s="5" t="n"/>
-      <c r="O9" s="5" t="n"/>
-    </row>
-    <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="1" t="n"/>
-      <c r="B10" s="1" t="n"/>
-      <c r="C10" s="1" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n"/>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="5" t="n"/>
-      <c r="K10" s="5" t="n"/>
-      <c r="L10" s="5" t="n"/>
-      <c r="M10" s="5" t="n"/>
-      <c r="N10" s="5" t="n"/>
-      <c r="O10" s="5" t="n"/>
-    </row>
-    <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="1" t="n"/>
-      <c r="C11" s="1" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="5" t="n"/>
-      <c r="H11" s="5" t="n"/>
-      <c r="I11" s="5" t="n"/>
-      <c r="J11" s="5" t="n"/>
-      <c r="K11" s="5" t="n"/>
-      <c r="L11" s="5" t="n"/>
-      <c r="M11" s="5" t="n"/>
-      <c r="N11" s="5" t="n"/>
-      <c r="O11" s="5" t="n"/>
-    </row>
-    <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="7" t="n"/>
-      <c r="B12" s="7" t="n"/>
-      <c r="C12" s="7" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="5" t="n"/>
-      <c r="H12" s="5" t="n"/>
-      <c r="I12" s="5" t="n"/>
-      <c r="J12" s="5" t="n"/>
-      <c r="K12" s="5" t="n"/>
-      <c r="L12" s="5" t="n"/>
-      <c r="M12" s="5" t="n"/>
-      <c r="N12" s="5" t="n"/>
-      <c r="O12" s="5" t="n"/>
-    </row>
-    <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="4" t="n"/>
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="4" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="5" t="n"/>
-      <c r="I13" s="5" t="n"/>
-      <c r="J13" s="5" t="n"/>
-      <c r="K13" s="5" t="n"/>
-      <c r="L13" s="5" t="n"/>
-      <c r="M13" s="5" t="n"/>
-      <c r="N13" s="5" t="n"/>
-      <c r="O13" s="5" t="n"/>
-    </row>
-    <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="1" t="n"/>
-      <c r="B14" s="1" t="n"/>
-      <c r="C14" s="1" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="5" t="n"/>
-      <c r="H14" s="5" t="n"/>
-      <c r="I14" s="5" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="5" t="n"/>
-      <c r="L14" s="5" t="n"/>
-      <c r="M14" s="5" t="n"/>
-      <c r="N14" s="5" t="n"/>
-      <c r="O14" s="5" t="n"/>
-    </row>
-    <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="1" t="n"/>
-      <c r="B15" s="1" t="n"/>
-      <c r="C15" s="1" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="5" t="n"/>
-      <c r="I15" s="5" t="n"/>
-      <c r="J15" s="5" t="n"/>
-      <c r="K15" s="5" t="n"/>
-      <c r="L15" s="5" t="n"/>
-      <c r="M15" s="5" t="n"/>
-      <c r="N15" s="5" t="n"/>
-      <c r="O15" s="5" t="n"/>
-    </row>
-    <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="8" t="n"/>
-      <c r="B16" s="8" t="n"/>
-      <c r="C16" s="8" t="n"/>
-    </row>
-    <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="9" t="n"/>
-      <c r="B17" s="9" t="n"/>
-      <c r="C17" s="9" t="n"/>
-    </row>
-    <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="9" t="n"/>
-      <c r="B18" s="9" t="n"/>
-      <c r="C18" s="9" t="n"/>
-    </row>
-    <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="9" t="n"/>
-      <c r="B19" s="9" t="n"/>
-      <c r="C19" s="9" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5" t="n"/>
-    </row>
-    <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="9" t="n"/>
-      <c r="B20" s="9" t="n"/>
-      <c r="C20" s="9" t="n"/>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="9" t="n"/>
-      <c r="B21" s="9" t="n"/>
-      <c r="C21" s="9" t="n"/>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="9" t="n"/>
-      <c r="B22" s="9" t="n"/>
-      <c r="C22" s="9" t="n"/>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="9" t="n"/>
-      <c r="B23" s="9" t="n"/>
-      <c r="C23" s="9" t="n"/>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="9" t="n"/>
-      <c r="B24" s="9" t="n"/>
-      <c r="C24" s="9" t="n"/>
-    </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="9" t="n"/>
-      <c r="B25" s="9" t="n"/>
-      <c r="C25" s="9" t="n"/>
-      <c r="E25" s="5" t="n"/>
-    </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="10" t="n"/>
-      <c r="B26" s="10" t="n"/>
-      <c r="C26" s="10" t="n"/>
-      <c r="E26" s="5" t="n"/>
-    </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="10" t="n"/>
-      <c r="B27" s="10" t="n"/>
-      <c r="C27" s="10" t="n"/>
-      <c r="E27" s="5" t="n"/>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="10" t="n"/>
-      <c r="B28" s="10" t="n"/>
-      <c r="C28" s="10" t="n"/>
-      <c r="E28" s="5" t="n"/>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="10" t="n"/>
-      <c r="B29" s="10" t="n"/>
-      <c r="C29" s="10" t="n"/>
-    </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="10" t="n"/>
-      <c r="B30" s="10" t="n"/>
-      <c r="C30" s="10" t="n"/>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="10" t="n"/>
-      <c r="B31" s="10" t="n"/>
-      <c r="C31" s="10" t="n"/>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="11" t="n"/>
-      <c r="B32" s="11" t="n"/>
-      <c r="C32" s="11" t="n"/>
-    </row>
-    <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="11" t="n"/>
-      <c r="B33" s="11" t="n"/>
-      <c r="C33" s="11" t="n"/>
-    </row>
-    <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="11" t="n"/>
-      <c r="B34" s="11" t="n"/>
-      <c r="C34" s="11" t="n"/>
-    </row>
-    <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="11" t="n"/>
-      <c r="B35" s="11" t="n"/>
-      <c r="C35" s="11" t="n"/>
-    </row>
-    <row r="36" ht="15.75" customHeight="1"/>
-    <row r="37" ht="15.75" customHeight="1"/>
-    <row r="38" ht="15.75" customHeight="1"/>
-    <row r="39" ht="15.75" customHeight="1"/>
-    <row r="40" ht="15.75" customHeight="1"/>
-    <row r="41" ht="15.75" customHeight="1"/>
-    <row r="42" ht="15.75" customHeight="1"/>
-    <row r="43" ht="15.75" customHeight="1"/>
-    <row r="44" ht="15.75" customHeight="1"/>
-    <row r="45" ht="15.75" customHeight="1"/>
-    <row r="46" ht="15.75" customHeight="1"/>
-    <row r="47" ht="15.75" customHeight="1"/>
-    <row r="48" ht="15.75" customHeight="1"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
+    </row>
+    <row r="7" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="4"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5"/>
+      <c r="L7" s="5"/>
+      <c r="M7" s="5"/>
+      <c r="N7" s="5"/>
+      <c r="O7" s="5"/>
+    </row>
+    <row r="8" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="5"/>
+    </row>
+    <row r="9" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5"/>
+      <c r="M9" s="5"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
+    </row>
+    <row r="10" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="5"/>
+      <c r="M10" s="5"/>
+      <c r="N10" s="5"/>
+      <c r="O10" s="5"/>
+    </row>
+    <row r="11" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="5"/>
+      <c r="M11" s="5"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="5"/>
+    </row>
+    <row r="12" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5"/>
+      <c r="L12" s="5"/>
+      <c r="M12" s="5"/>
+      <c r="N12" s="5"/>
+      <c r="O12" s="5"/>
+    </row>
+    <row r="13" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="5"/>
+      <c r="N13" s="5"/>
+      <c r="O13" s="5"/>
+    </row>
+    <row r="14" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
+      <c r="M14" s="5"/>
+      <c r="N14" s="5"/>
+      <c r="O14" s="5"/>
+    </row>
+    <row r="15" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="5"/>
+      <c r="M15" s="5"/>
+      <c r="N15" s="5"/>
+      <c r="O15" s="5"/>
+    </row>
+    <row r="16" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+    </row>
+    <row r="17" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A17" s="9"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+    </row>
+    <row r="18" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A18" s="9"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+    </row>
+    <row r="19" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A19" s="9"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+    </row>
+    <row r="20" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A20" s="9"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+    </row>
+    <row r="21" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A21" s="9"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+    </row>
+    <row r="22" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A22" s="9"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+    </row>
+    <row r="23" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A23" s="9"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
+    </row>
+    <row r="24" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A24" s="9"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+    </row>
+    <row r="25" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A25" s="9"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="E25" s="5"/>
+    </row>
+    <row r="26" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A26" s="10"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="10"/>
+      <c r="E26" s="5"/>
+    </row>
+    <row r="27" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A27" s="10"/>
+      <c r="B27" s="10"/>
+      <c r="C27" s="10"/>
+      <c r="E27" s="5"/>
+    </row>
+    <row r="28" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A28" s="10"/>
+      <c r="B28" s="10"/>
+      <c r="C28" s="10"/>
+      <c r="E28" s="5"/>
+    </row>
+    <row r="29" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A29" s="10"/>
+      <c r="B29" s="10"/>
+      <c r="C29" s="10"/>
+    </row>
+    <row r="30" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A30" s="10"/>
+      <c r="B30" s="10"/>
+      <c r="C30" s="10"/>
+    </row>
+    <row r="31" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A31" s="10"/>
+      <c r="B31" s="10"/>
+      <c r="C31" s="10"/>
+    </row>
+    <row r="32" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A32" s="11"/>
+      <c r="B32" s="11"/>
+      <c r="C32" s="11"/>
+    </row>
+    <row r="33" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A33" s="11"/>
+      <c r="B33" s="11"/>
+      <c r="C33" s="11"/>
+    </row>
+    <row r="34" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A34" s="11"/>
+      <c r="B34" s="11"/>
+      <c r="C34" s="11"/>
+    </row>
+    <row r="35" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A35" s="11"/>
+      <c r="B35" s="11"/>
+      <c r="C35" s="11"/>
+    </row>
+    <row r="36" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="37" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="38" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="39" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="40" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="41" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="42" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="43" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="44" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="45" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="46" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="47" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="48" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="49" ht="15.75" customHeight="1"/>
     <row r="50" ht="15.75" customHeight="1"/>
     <row r="51" ht="15.75" customHeight="1"/>
@@ -1912,7 +1874,8 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/OO_Ingredient.xlsx
+++ b/JsonConverter/ExcelFiles/OO_Ingredient.xlsx
@@ -1,169 +1,90 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="12770" yWindow="2240" windowWidth="19820" windowHeight="18420"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="12770" yWindow="2240" windowWidth="19820" windowHeight="18420" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="DNTable_Ingredient" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DNTable_Ingredient" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="25">
-  <si>
-    <t>재료 고유 ID</t>
-  </si>
-  <si>
-    <t>재료 이름</t>
-  </si>
-  <si>
-    <t>재료 설명</t>
-  </si>
-  <si>
-    <t>아이콘 리소스 경로</t>
-  </si>
-  <si>
-    <t>재료 등급</t>
-  </si>
-  <si>
-    <t>최대 중첩 수</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>Id</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>IconPath</t>
-  </si>
-  <si>
-    <t>Grade</t>
-  </si>
-  <si>
-    <t>MaxStackCount</t>
-  </si>
-  <si>
-    <t>쌀</t>
-  </si>
-  <si>
-    <t>춘향의 아버님이 내어주신 기름진 쌀. 모란의 기계 솥을 거치면 백성들의 허기를 단숨에 채워줄 따스한 밥과 떡이 된다.</t>
-  </si>
-  <si>
-    <t>일반</t>
-  </si>
-  <si>
-    <t>Ing_Pumpkin_01</t>
-  </si>
-  <si>
-    <t>호박</t>
-  </si>
-  <si>
-    <t>굶주린 동쪽 마을 마당구석에서 자라난 호박. 쌀과 함께 푹 고아내면 얼어붙은 몸을 녹이는 달콤한 호박죽이 완성된다.</t>
-  </si>
-  <si>
-    <t>채소</t>
-  </si>
-  <si>
-    <t>모란의 집 텃밭에서 정성껏 기른 소박한 채소 바구니. 비록 재익 군이 다른 음식을 다 먹어치우는 바람에 이것만 남았지만, 갓 따낸 싱그러운 생기가 가득하다.</t>
-  </si>
-  <si>
-    <t>조기</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ing_Veggie_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ing_Rice_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="10">
     <font>
+      <name val="Arial"/>
+      <color rgb="FF000000"/>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="&quot;맑은 고딕&quot;"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <color rgb="FF000000"/>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="&quot;맑은 고딕&quot;"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="10"/>
     </font>
     <font>
+      <name val="&quot;맑은 고딕&quot;"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <color rgb="FF008000"/>
       <sz val="11"/>
-      <color rgb="FF008000"/>
-      <name val="&quot;맑은 고딕&quot;"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
     </font>
     <font>
+      <name val="Arial"/>
+      <charset val="129"/>
+      <family val="3"/>
       <sz val="8"/>
-      <name val="Arial"/>
-      <family val="3"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <color rgb="FF000000"/>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
+      <name val="Arial"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <color rgb="FF000000"/>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="3"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="11">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -194,14 +115,29 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
+        <fgColor theme="7" tint="0.7999816888943144"/>
         <bgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
+        <fgColor theme="7" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2F0D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -247,48 +183,122 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="22">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -489,438 +499,509 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1000"/>
-  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
+  <dimension ref="A1:O35"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="20" style="3" customWidth="1"/>
-    <col min="2" max="2" width="16" style="3" customWidth="1"/>
-    <col min="3" max="3" width="80" style="3" customWidth="1"/>
-    <col min="4" max="4" width="28" style="3" customWidth="1"/>
-    <col min="5" max="5" width="14" style="3" customWidth="1"/>
-    <col min="6" max="6" width="16" style="3" customWidth="1"/>
-    <col min="7" max="7" width="12.54296875" style="3" customWidth="1"/>
-    <col min="8" max="16384" width="12.54296875" style="3"/>
+    <col width="14" customWidth="1" style="3" min="1" max="1"/>
+    <col width="14" customWidth="1" style="3" min="2" max="2"/>
+    <col width="14" customWidth="1" style="3" min="3" max="3"/>
+    <col width="16" customWidth="1" style="3" min="4" max="4"/>
+    <col width="14" customWidth="1" style="3" min="5" max="5"/>
+    <col width="14" customWidth="1" style="3" min="6" max="6"/>
+    <col width="12.54296875" customWidth="1" style="3" min="7" max="7"/>
+    <col width="12.54296875" customWidth="1" style="3" min="8" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" ht="13" customHeight="1">
-      <c r="A2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" s="13" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A3" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="14" t="s">
+    <row r="1" ht="15.75" customHeight="1">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>재료 고유 ID</t>
+        </is>
+      </c>
+      <c r="B1" s="18" t="inlineStr">
+        <is>
+          <t>재료 이름</t>
+        </is>
+      </c>
+      <c r="C1" s="18" t="inlineStr">
+        <is>
+          <t>재료 설명</t>
+        </is>
+      </c>
+      <c r="D1" s="18" t="inlineStr">
+        <is>
+          <t>아이콘 리소스 경로</t>
+        </is>
+      </c>
+      <c r="E1" s="18" t="inlineStr">
+        <is>
+          <t>재료 등급</t>
+        </is>
+      </c>
+      <c r="F1" s="19" t="inlineStr">
+        <is>
+          <t>최대 중첩 수</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="13" customHeight="1">
+      <c r="A2" s="20" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="B2" s="20" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C2" s="20" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D2" s="20" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E2" s="20" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F2" s="20" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15.75" customFormat="1" customHeight="1" s="13">
+      <c r="A3" s="21" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="B3" s="21" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C3" s="21" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D3" s="21" t="inlineStr">
+        <is>
+          <t>IconPath</t>
+        </is>
+      </c>
+      <c r="E3" s="21" t="inlineStr">
+        <is>
+          <t>Grade</t>
+        </is>
+      </c>
+      <c r="F3" s="21" t="inlineStr">
+        <is>
+          <t>MaxStackCount</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15.75" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Ing_Rice_01</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>쌀</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>춘향의 아버님이 내어주신 기름진 쌀. 모란의 기계 솥을 거치면 백성들의 허기를 단숨에 채워줄 따스한 밥과 떡이 된다.</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Images/Food/Rice</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="F4" s="16" t="n">
         <v>12</v>
       </c>
-      <c r="F3" s="15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A4" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" s="16">
-        <v>99</v>
-      </c>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
-    </row>
-    <row r="5" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A5" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" s="5">
-        <v>99</v>
-      </c>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
-    </row>
-    <row r="6" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A6" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F6" s="5">
-        <v>99</v>
-      </c>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="5"/>
-      <c r="O6" s="5"/>
-    </row>
-    <row r="7" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
-      <c r="M7" s="5"/>
-      <c r="N7" s="5"/>
-      <c r="O7" s="5"/>
-    </row>
-    <row r="8" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
-      <c r="M8" s="5"/>
-      <c r="N8" s="5"/>
-      <c r="O8" s="5"/>
-    </row>
-    <row r="9" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5"/>
-      <c r="M9" s="5"/>
-      <c r="N9" s="5"/>
-      <c r="O9" s="5"/>
-    </row>
-    <row r="10" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
-      <c r="L10" s="5"/>
-      <c r="M10" s="5"/>
-      <c r="N10" s="5"/>
-      <c r="O10" s="5"/>
-    </row>
-    <row r="11" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5"/>
-      <c r="L11" s="5"/>
-      <c r="M11" s="5"/>
-      <c r="N11" s="5"/>
-      <c r="O11" s="5"/>
-    </row>
-    <row r="12" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5"/>
-      <c r="L12" s="5"/>
-      <c r="M12" s="5"/>
-      <c r="N12" s="5"/>
-      <c r="O12" s="5"/>
-    </row>
-    <row r="13" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
-      <c r="L13" s="5"/>
-      <c r="M13" s="5"/>
-      <c r="N13" s="5"/>
-      <c r="O13" s="5"/>
-    </row>
-    <row r="14" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
-      <c r="L14" s="5"/>
-      <c r="M14" s="5"/>
-      <c r="N14" s="5"/>
-      <c r="O14" s="5"/>
-    </row>
-    <row r="15" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5"/>
-      <c r="L15" s="5"/>
-      <c r="M15" s="5"/>
-      <c r="N15" s="5"/>
-      <c r="O15" s="5"/>
-    </row>
-    <row r="16" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-    </row>
-    <row r="17" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-    </row>
-    <row r="18" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-    </row>
-    <row r="19" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-    </row>
-    <row r="20" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-    </row>
-    <row r="21" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A21" s="9"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-    </row>
-    <row r="22" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A22" s="9"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-    </row>
-    <row r="23" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A23" s="9"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-    </row>
-    <row r="24" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A24" s="9"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-    </row>
-    <row r="25" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A25" s="9"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="E25" s="5"/>
-    </row>
-    <row r="26" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A26" s="10"/>
-      <c r="B26" s="10"/>
-      <c r="C26" s="10"/>
-      <c r="E26" s="5"/>
-    </row>
-    <row r="27" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A27" s="10"/>
-      <c r="B27" s="10"/>
-      <c r="C27" s="10"/>
-      <c r="E27" s="5"/>
-    </row>
-    <row r="28" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A28" s="10"/>
-      <c r="B28" s="10"/>
-      <c r="C28" s="10"/>
-      <c r="E28" s="5"/>
-    </row>
-    <row r="29" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A29" s="10"/>
-      <c r="B29" s="10"/>
-      <c r="C29" s="10"/>
-    </row>
-    <row r="30" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A30" s="10"/>
-      <c r="B30" s="10"/>
-      <c r="C30" s="10"/>
-    </row>
-    <row r="31" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A31" s="10"/>
-      <c r="B31" s="10"/>
-      <c r="C31" s="10"/>
-    </row>
-    <row r="32" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A32" s="11"/>
-      <c r="B32" s="11"/>
-      <c r="C32" s="11"/>
-    </row>
-    <row r="33" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A33" s="11"/>
-      <c r="B33" s="11"/>
-      <c r="C33" s="11"/>
-    </row>
-    <row r="34" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A34" s="11"/>
-      <c r="B34" s="11"/>
-      <c r="C34" s="11"/>
-    </row>
-    <row r="35" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A35" s="11"/>
-      <c r="B35" s="11"/>
-      <c r="C35" s="11"/>
-    </row>
-    <row r="36" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="37" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="38" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="39" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="40" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="41" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="42" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="43" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="44" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="45" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="46" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="47" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="48" spans="1:3" ht="15.75" customHeight="1"/>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
+      <c r="I4" s="5" t="n"/>
+      <c r="J4" s="5" t="n"/>
+      <c r="K4" s="5" t="n"/>
+      <c r="L4" s="5" t="n"/>
+      <c r="M4" s="5" t="n"/>
+      <c r="N4" s="5" t="n"/>
+      <c r="O4" s="5" t="n"/>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="17" t="inlineStr">
+        <is>
+          <t>Ing_Veggie_01</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>채소</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>동쪽 마을에서 얻은 싱싱한 채소. 손질한 뒤 쌀과 함께 끓이면 따뜻한 채소죽이 된다.</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Images/Food/Vegetable</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="15.75" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Ing_Pumpkin_01</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>호박</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>나중에 호박죽과 다른 요리에 쓰일 달큰한 호박.</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Images/Food/Pumpkin</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="n"/>
+      <c r="N6" s="5" t="n"/>
+      <c r="O6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="15.75" customHeight="1">
+      <c r="A7" s="4" t="n"/>
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n"/>
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="5" t="n"/>
+      <c r="K7" s="5" t="n"/>
+      <c r="L7" s="5" t="n"/>
+      <c r="M7" s="5" t="n"/>
+      <c r="N7" s="5" t="n"/>
+      <c r="O7" s="5" t="n"/>
+    </row>
+    <row r="8" ht="15.75" customHeight="1">
+      <c r="A8" s="7" t="n"/>
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="7" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="5" t="n"/>
+      <c r="K8" s="5" t="n"/>
+      <c r="L8" s="5" t="n"/>
+      <c r="M8" s="5" t="n"/>
+      <c r="N8" s="5" t="n"/>
+      <c r="O8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="15.75" customHeight="1">
+      <c r="A9" s="7" t="n"/>
+      <c r="B9" s="7" t="n"/>
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="5" t="n"/>
+      <c r="J9" s="5" t="n"/>
+      <c r="K9" s="5" t="n"/>
+      <c r="L9" s="5" t="n"/>
+      <c r="M9" s="5" t="n"/>
+      <c r="N9" s="5" t="n"/>
+      <c r="O9" s="5" t="n"/>
+    </row>
+    <row r="10" ht="15.75" customHeight="1">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="1" t="n"/>
+      <c r="C10" s="1" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n"/>
+      <c r="I10" s="5" t="n"/>
+      <c r="J10" s="5" t="n"/>
+      <c r="K10" s="5" t="n"/>
+      <c r="L10" s="5" t="n"/>
+      <c r="M10" s="5" t="n"/>
+      <c r="N10" s="5" t="n"/>
+      <c r="O10" s="5" t="n"/>
+    </row>
+    <row r="11" ht="15.75" customHeight="1">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="1" t="n"/>
+      <c r="C11" s="1" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="n"/>
+      <c r="I11" s="5" t="n"/>
+      <c r="J11" s="5" t="n"/>
+      <c r="K11" s="5" t="n"/>
+      <c r="L11" s="5" t="n"/>
+      <c r="M11" s="5" t="n"/>
+      <c r="N11" s="5" t="n"/>
+      <c r="O11" s="5" t="n"/>
+    </row>
+    <row r="12" ht="15.75" customHeight="1">
+      <c r="A12" s="7" t="n"/>
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="7" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n"/>
+      <c r="I12" s="5" t="n"/>
+      <c r="J12" s="5" t="n"/>
+      <c r="K12" s="5" t="n"/>
+      <c r="L12" s="5" t="n"/>
+      <c r="M12" s="5" t="n"/>
+      <c r="N12" s="5" t="n"/>
+      <c r="O12" s="5" t="n"/>
+    </row>
+    <row r="13" ht="15.75" customHeight="1">
+      <c r="A13" s="4" t="n"/>
+      <c r="B13" s="4" t="n"/>
+      <c r="C13" s="4" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="5" t="n"/>
+      <c r="I13" s="5" t="n"/>
+      <c r="J13" s="5" t="n"/>
+      <c r="K13" s="5" t="n"/>
+      <c r="L13" s="5" t="n"/>
+      <c r="M13" s="5" t="n"/>
+      <c r="N13" s="5" t="n"/>
+      <c r="O13" s="5" t="n"/>
+    </row>
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="1" t="n"/>
+      <c r="C14" s="1" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n"/>
+      <c r="I14" s="5" t="n"/>
+      <c r="J14" s="5" t="n"/>
+      <c r="K14" s="5" t="n"/>
+      <c r="L14" s="5" t="n"/>
+      <c r="M14" s="5" t="n"/>
+      <c r="N14" s="5" t="n"/>
+      <c r="O14" s="5" t="n"/>
+    </row>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="1" t="n"/>
+      <c r="C15" s="1" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="n"/>
+      <c r="I15" s="5" t="n"/>
+      <c r="J15" s="5" t="n"/>
+      <c r="K15" s="5" t="n"/>
+      <c r="L15" s="5" t="n"/>
+      <c r="M15" s="5" t="n"/>
+      <c r="N15" s="5" t="n"/>
+      <c r="O15" s="5" t="n"/>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="8" t="n"/>
+      <c r="B16" s="8" t="n"/>
+      <c r="C16" s="8" t="n"/>
+    </row>
+    <row r="17" ht="15.75" customHeight="1">
+      <c r="A17" s="9" t="n"/>
+      <c r="B17" s="9" t="n"/>
+      <c r="C17" s="9" t="n"/>
+    </row>
+    <row r="18" ht="15.75" customHeight="1">
+      <c r="A18" s="9" t="n"/>
+      <c r="B18" s="9" t="n"/>
+      <c r="C18" s="9" t="n"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1">
+      <c r="A19" s="9" t="n"/>
+      <c r="B19" s="9" t="n"/>
+      <c r="C19" s="9" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+    </row>
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="A20" s="9" t="n"/>
+      <c r="B20" s="9" t="n"/>
+      <c r="C20" s="9" t="n"/>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="9" t="n"/>
+      <c r="B21" s="9" t="n"/>
+      <c r="C21" s="9" t="n"/>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="9" t="n"/>
+      <c r="B22" s="9" t="n"/>
+      <c r="C22" s="9" t="n"/>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="9" t="n"/>
+      <c r="B23" s="9" t="n"/>
+      <c r="C23" s="9" t="n"/>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="9" t="n"/>
+      <c r="B24" s="9" t="n"/>
+      <c r="C24" s="9" t="n"/>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="9" t="n"/>
+      <c r="B25" s="9" t="n"/>
+      <c r="C25" s="9" t="n"/>
+      <c r="E25" s="5" t="n"/>
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="10" t="n"/>
+      <c r="B26" s="10" t="n"/>
+      <c r="C26" s="10" t="n"/>
+      <c r="E26" s="5" t="n"/>
+    </row>
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="10" t="n"/>
+      <c r="B27" s="10" t="n"/>
+      <c r="C27" s="10" t="n"/>
+      <c r="E27" s="5" t="n"/>
+    </row>
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="10" t="n"/>
+      <c r="B28" s="10" t="n"/>
+      <c r="C28" s="10" t="n"/>
+      <c r="E28" s="5" t="n"/>
+    </row>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="10" t="n"/>
+      <c r="B29" s="10" t="n"/>
+      <c r="C29" s="10" t="n"/>
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="10" t="n"/>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+    </row>
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="10" t="n"/>
+      <c r="B31" s="10" t="n"/>
+      <c r="C31" s="10" t="n"/>
+    </row>
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="11" t="n"/>
+      <c r="B32" s="11" t="n"/>
+      <c r="C32" s="11" t="n"/>
+    </row>
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="A33" s="11" t="n"/>
+      <c r="B33" s="11" t="n"/>
+      <c r="C33" s="11" t="n"/>
+    </row>
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="A34" s="11" t="n"/>
+      <c r="B34" s="11" t="n"/>
+      <c r="C34" s="11" t="n"/>
+    </row>
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="A35" s="11" t="n"/>
+      <c r="B35" s="11" t="n"/>
+      <c r="C35" s="11" t="n"/>
+    </row>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="15.75" customHeight="1"/>
+    <row r="38" ht="15.75" customHeight="1"/>
+    <row r="39" ht="15.75" customHeight="1"/>
+    <row r="40" ht="15.75" customHeight="1"/>
+    <row r="41" ht="15.75" customHeight="1"/>
+    <row r="42" ht="15.75" customHeight="1"/>
+    <row r="43" ht="15.75" customHeight="1"/>
+    <row r="44" ht="15.75" customHeight="1"/>
+    <row r="45" ht="15.75" customHeight="1"/>
+    <row r="46" ht="15.75" customHeight="1"/>
+    <row r="47" ht="15.75" customHeight="1"/>
+    <row r="48" ht="15.75" customHeight="1"/>
     <row r="49" ht="15.75" customHeight="1"/>
     <row r="50" ht="15.75" customHeight="1"/>
     <row r="51" ht="15.75" customHeight="1"/>
@@ -1874,8 +1955,7 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/OO_Ingredient.xlsx
+++ b/JsonConverter/ExcelFiles/OO_Ingredient.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O35"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="14" customWidth="1" style="3" min="1" max="1"/>
@@ -614,381 +614,153 @@
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Ing_Rice_01</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>쌀</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>춘향의 아버님이 내어주신 기름진 쌀. 모란의 기계 솥을 거치면 백성들의 허기를 단숨에 채워줄 따스한 밥과 떡이 된다.</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Images/Food/Rice</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>일반</t>
         </is>
       </c>
-      <c r="F4" s="16" t="n">
+      <c r="F4" t="n">
         <v>12</v>
       </c>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="5" t="n"/>
-      <c r="I4" s="5" t="n"/>
-      <c r="J4" s="5" t="n"/>
-      <c r="K4" s="5" t="n"/>
-      <c r="L4" s="5" t="n"/>
-      <c r="M4" s="5" t="n"/>
-      <c r="N4" s="5" t="n"/>
-      <c r="O4" s="5" t="n"/>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Ing_Veggie_01</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>채소</t>
         </is>
       </c>
-      <c r="C5" s="17" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>동쪽 마을에서 얻은 싱싱한 채소. 손질한 뒤 쌀과 함께 끓이면 따뜻한 채소죽이 된다.</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Images/Food/Vegetable</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>일반</t>
         </is>
       </c>
-      <c r="F5" s="5" t="n">
+      <c r="F5" t="n">
         <v>12</v>
       </c>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="5" t="n"/>
-      <c r="I5" s="5" t="n"/>
-      <c r="J5" s="5" t="n"/>
-      <c r="K5" s="5" t="n"/>
-      <c r="L5" s="5" t="n"/>
-      <c r="M5" s="5" t="n"/>
-      <c r="N5" s="5" t="n"/>
-      <c r="O5" s="5" t="n"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Ing_Pumpkin_01</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>호박</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>나중에 호박죽과 다른 요리에 쓰일 달큰한 호박.</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Images/Food/Pumpkin</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>일반</t>
         </is>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="F6" t="n">
         <v>12</v>
       </c>
-      <c r="G6" s="5" t="n"/>
-      <c r="H6" s="5" t="n"/>
-      <c r="I6" s="5" t="n"/>
-      <c r="J6" s="5" t="n"/>
-      <c r="K6" s="5" t="n"/>
-      <c r="L6" s="5" t="n"/>
-      <c r="M6" s="5" t="n"/>
-      <c r="N6" s="5" t="n"/>
-      <c r="O6" s="5" t="n"/>
     </row>
     <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="4" t="n"/>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="5" t="n"/>
-      <c r="H7" s="5" t="n"/>
-      <c r="I7" s="5" t="n"/>
-      <c r="J7" s="5" t="n"/>
-      <c r="K7" s="5" t="n"/>
-      <c r="L7" s="5" t="n"/>
-      <c r="M7" s="5" t="n"/>
-      <c r="N7" s="5" t="n"/>
-      <c r="O7" s="5" t="n"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Ing_ChiliPepper_01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>청양고추</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>청양고추</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Images/Food/ChiliPepper</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>99</v>
+      </c>
     </row>
-    <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="7" t="n"/>
-      <c r="B8" s="7" t="n"/>
-      <c r="C8" s="7" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n"/>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="5" t="n"/>
-      <c r="K8" s="5" t="n"/>
-      <c r="L8" s="5" t="n"/>
-      <c r="M8" s="5" t="n"/>
-      <c r="N8" s="5" t="n"/>
-      <c r="O8" s="5" t="n"/>
-    </row>
-    <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="7" t="n"/>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="5" t="n"/>
-      <c r="I9" s="5" t="n"/>
-      <c r="J9" s="5" t="n"/>
-      <c r="K9" s="5" t="n"/>
-      <c r="L9" s="5" t="n"/>
-      <c r="M9" s="5" t="n"/>
-      <c r="N9" s="5" t="n"/>
-      <c r="O9" s="5" t="n"/>
-    </row>
-    <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="1" t="n"/>
-      <c r="B10" s="1" t="n"/>
-      <c r="C10" s="1" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n"/>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="5" t="n"/>
-      <c r="K10" s="5" t="n"/>
-      <c r="L10" s="5" t="n"/>
-      <c r="M10" s="5" t="n"/>
-      <c r="N10" s="5" t="n"/>
-      <c r="O10" s="5" t="n"/>
-    </row>
-    <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="1" t="n"/>
-      <c r="C11" s="1" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="5" t="n"/>
-      <c r="H11" s="5" t="n"/>
-      <c r="I11" s="5" t="n"/>
-      <c r="J11" s="5" t="n"/>
-      <c r="K11" s="5" t="n"/>
-      <c r="L11" s="5" t="n"/>
-      <c r="M11" s="5" t="n"/>
-      <c r="N11" s="5" t="n"/>
-      <c r="O11" s="5" t="n"/>
-    </row>
-    <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="7" t="n"/>
-      <c r="B12" s="7" t="n"/>
-      <c r="C12" s="7" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="5" t="n"/>
-      <c r="H12" s="5" t="n"/>
-      <c r="I12" s="5" t="n"/>
-      <c r="J12" s="5" t="n"/>
-      <c r="K12" s="5" t="n"/>
-      <c r="L12" s="5" t="n"/>
-      <c r="M12" s="5" t="n"/>
-      <c r="N12" s="5" t="n"/>
-      <c r="O12" s="5" t="n"/>
-    </row>
-    <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="4" t="n"/>
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="4" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="5" t="n"/>
-      <c r="I13" s="5" t="n"/>
-      <c r="J13" s="5" t="n"/>
-      <c r="K13" s="5" t="n"/>
-      <c r="L13" s="5" t="n"/>
-      <c r="M13" s="5" t="n"/>
-      <c r="N13" s="5" t="n"/>
-      <c r="O13" s="5" t="n"/>
-    </row>
-    <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="1" t="n"/>
-      <c r="B14" s="1" t="n"/>
-      <c r="C14" s="1" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="5" t="n"/>
-      <c r="H14" s="5" t="n"/>
-      <c r="I14" s="5" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="5" t="n"/>
-      <c r="L14" s="5" t="n"/>
-      <c r="M14" s="5" t="n"/>
-      <c r="N14" s="5" t="n"/>
-      <c r="O14" s="5" t="n"/>
-    </row>
-    <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="1" t="n"/>
-      <c r="B15" s="1" t="n"/>
-      <c r="C15" s="1" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="5" t="n"/>
-      <c r="I15" s="5" t="n"/>
-      <c r="J15" s="5" t="n"/>
-      <c r="K15" s="5" t="n"/>
-      <c r="L15" s="5" t="n"/>
-      <c r="M15" s="5" t="n"/>
-      <c r="N15" s="5" t="n"/>
-      <c r="O15" s="5" t="n"/>
-    </row>
-    <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="8" t="n"/>
-      <c r="B16" s="8" t="n"/>
-      <c r="C16" s="8" t="n"/>
-    </row>
-    <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="9" t="n"/>
-      <c r="B17" s="9" t="n"/>
-      <c r="C17" s="9" t="n"/>
-    </row>
-    <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="9" t="n"/>
-      <c r="B18" s="9" t="n"/>
-      <c r="C18" s="9" t="n"/>
-    </row>
-    <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="9" t="n"/>
-      <c r="B19" s="9" t="n"/>
-      <c r="C19" s="9" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5" t="n"/>
-    </row>
-    <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="9" t="n"/>
-      <c r="B20" s="9" t="n"/>
-      <c r="C20" s="9" t="n"/>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="9" t="n"/>
-      <c r="B21" s="9" t="n"/>
-      <c r="C21" s="9" t="n"/>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="9" t="n"/>
-      <c r="B22" s="9" t="n"/>
-      <c r="C22" s="9" t="n"/>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="9" t="n"/>
-      <c r="B23" s="9" t="n"/>
-      <c r="C23" s="9" t="n"/>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="9" t="n"/>
-      <c r="B24" s="9" t="n"/>
-      <c r="C24" s="9" t="n"/>
-    </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="9" t="n"/>
-      <c r="B25" s="9" t="n"/>
-      <c r="C25" s="9" t="n"/>
-      <c r="E25" s="5" t="n"/>
-    </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="10" t="n"/>
-      <c r="B26" s="10" t="n"/>
-      <c r="C26" s="10" t="n"/>
-      <c r="E26" s="5" t="n"/>
-    </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="10" t="n"/>
-      <c r="B27" s="10" t="n"/>
-      <c r="C27" s="10" t="n"/>
-      <c r="E27" s="5" t="n"/>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="10" t="n"/>
-      <c r="B28" s="10" t="n"/>
-      <c r="C28" s="10" t="n"/>
-      <c r="E28" s="5" t="n"/>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="10" t="n"/>
-      <c r="B29" s="10" t="n"/>
-      <c r="C29" s="10" t="n"/>
-    </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="10" t="n"/>
-      <c r="B30" s="10" t="n"/>
-      <c r="C30" s="10" t="n"/>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="10" t="n"/>
-      <c r="B31" s="10" t="n"/>
-      <c r="C31" s="10" t="n"/>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="11" t="n"/>
-      <c r="B32" s="11" t="n"/>
-      <c r="C32" s="11" t="n"/>
-    </row>
-    <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="11" t="n"/>
-      <c r="B33" s="11" t="n"/>
-      <c r="C33" s="11" t="n"/>
-    </row>
-    <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="11" t="n"/>
-      <c r="B34" s="11" t="n"/>
-      <c r="C34" s="11" t="n"/>
-    </row>
-    <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="11" t="n"/>
-      <c r="B35" s="11" t="n"/>
-      <c r="C35" s="11" t="n"/>
-    </row>
+    <row r="8" ht="15.75" customHeight="1"/>
+    <row r="9" ht="15.75" customHeight="1"/>
+    <row r="10" ht="15.75" customHeight="1"/>
+    <row r="11" ht="15.75" customHeight="1"/>
+    <row r="12" ht="15.75" customHeight="1"/>
+    <row r="13" ht="15.75" customHeight="1"/>
+    <row r="14" ht="15.75" customHeight="1"/>
+    <row r="15" ht="15.75" customHeight="1"/>
+    <row r="16" ht="15.75" customHeight="1"/>
+    <row r="17" ht="15.75" customHeight="1"/>
+    <row r="18" ht="15.75" customHeight="1"/>
+    <row r="19" ht="15.75" customHeight="1"/>
+    <row r="20" ht="15.75" customHeight="1"/>
+    <row r="21" ht="15.75" customHeight="1"/>
+    <row r="22" ht="15.75" customHeight="1"/>
+    <row r="23" ht="15.75" customHeight="1"/>
+    <row r="24" ht="15.75" customHeight="1"/>
+    <row r="25" ht="15.75" customHeight="1"/>
+    <row r="26" ht="15.75" customHeight="1"/>
+    <row r="27" ht="15.75" customHeight="1"/>
+    <row r="28" ht="15.75" customHeight="1"/>
+    <row r="29" ht="15.75" customHeight="1"/>
+    <row r="30" ht="15.75" customHeight="1"/>
+    <row r="31" ht="15.75" customHeight="1"/>
+    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1"/>
     <row r="36" ht="15.75" customHeight="1"/>
     <row r="37" ht="15.75" customHeight="1"/>
     <row r="38" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/OO_Ingredient.xlsx
+++ b/JsonConverter/ExcelFiles/OO_Ingredient.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="6">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
@@ -27,25 +27,6 @@
       <name val="&quot;맑은 고딕&quot;"/>
       <charset val="129"/>
       <family val="3"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="&quot;맑은 고딕&quot;"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <color rgb="FF008000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <family val="2"/>
       <color rgb="FF000000"/>
       <sz val="10"/>
     </font>
@@ -64,13 +45,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
-    </font>
-    <font>
       <name val="Arial"/>
       <charset val="129"/>
       <family val="3"/>
@@ -79,10 +53,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial"/>
+      <family val="2"/>
       <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -97,51 +74,27 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor rgb="FF4D93D9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor rgb="FFFFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor rgb="FFD86DCD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.7999816888943144"/>
-        <bgColor rgb="FFC6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9EAF7"/>
+        <fgColor rgb="FFD9EAF7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="FFFCE4D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2F0D9"/>
+        <fgColor rgb="FFE2F0D9"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -164,68 +117,29 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -504,110 +418,107 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="14" customWidth="1" style="3" min="1" max="1"/>
-    <col width="14" customWidth="1" style="3" min="2" max="2"/>
-    <col width="14" customWidth="1" style="3" min="3" max="3"/>
-    <col width="16" customWidth="1" style="3" min="4" max="4"/>
-    <col width="14" customWidth="1" style="3" min="5" max="5"/>
-    <col width="14" customWidth="1" style="3" min="6" max="6"/>
-    <col width="12.54296875" customWidth="1" style="3" min="7" max="7"/>
-    <col width="12.54296875" customWidth="1" style="3" min="8" max="16384"/>
+    <col width="14" customWidth="1" style="1" min="1" max="3"/>
+    <col width="16" customWidth="1" style="1" min="4" max="4"/>
+    <col width="14" customWidth="1" style="1" min="5" max="6"/>
+    <col width="12.54296875" customWidth="1" style="1" min="7" max="8"/>
+    <col width="12.54296875" customWidth="1" style="1" min="9" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="18" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>재료 고유 ID</t>
         </is>
       </c>
-      <c r="B1" s="18" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>재료 이름</t>
         </is>
       </c>
-      <c r="C1" s="18" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>재료 설명</t>
         </is>
       </c>
-      <c r="D1" s="18" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>아이콘 리소스 경로</t>
         </is>
       </c>
-      <c r="E1" s="18" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>재료 등급</t>
         </is>
       </c>
-      <c r="F1" s="19" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>최대 중첩 수</t>
         </is>
       </c>
     </row>
     <row r="2" ht="13" customHeight="1">
-      <c r="A2" s="20" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="B2" s="20" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="C2" s="20" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D2" s="20" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E2" s="20" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="F2" s="20" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15.75" customFormat="1" customHeight="1" s="13">
-      <c r="A3" s="21" t="inlineStr">
+    <row r="3" ht="15.75" customFormat="1" customHeight="1" s="2">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>Id</t>
         </is>
       </c>
-      <c r="B3" s="21" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C3" s="21" t="inlineStr">
+      <c r="C3" s="7" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D3" s="21" t="inlineStr">
+      <c r="D3" s="7" t="inlineStr">
         <is>
           <t>IconPath</t>
         </is>
       </c>
-      <c r="E3" s="21" t="inlineStr">
+      <c r="E3" s="7" t="inlineStr">
         <is>
           <t>Grade</t>
         </is>
       </c>
-      <c r="F3" s="21" t="inlineStr">
+      <c r="F3" s="7" t="inlineStr">
         <is>
           <t>MaxStackCount</t>
         </is>
@@ -656,7 +567,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>동쪽 마을에서 얻은 싱싱한 채소. 손질한 뒤 쌀과 함께 끓이면 따뜻한 채소죽이 된다.</t>
+          <t>?? ???? ?? ??? ??. ??? ? ?? ?? ??? ??? ???? ??.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -704,7 +615,7 @@
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Ing_ChiliPepper_01</t>
         </is>
@@ -733,9 +644,96 @@
         <v>99</v>
       </c>
     </row>
-    <row r="8" ht="15.75" customHeight="1"/>
-    <row r="9" ht="15.75" customHeight="1"/>
-    <row r="10" ht="15.75" customHeight="1"/>
+    <row r="8" ht="15.75" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Ing_Fish_01</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>???? ?? ??. ??? ??? ??? ??.</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Images/Food/Fish</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="9" ht="15.75" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Ing_Kimch_01</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>김치</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Stage1 보상으로 받은 김치. 얼큰한 찌개를 만들 때 깊은 맛을 더합니다.</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Images/Food/Kimch</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="10" ht="15.75" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>Ing_Honey_01</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>꿀</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>Stage2 보상으로 받는 달콤한 재료입니다.</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Images/Food/Honey</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>99</v>
+      </c>
+    </row>
     <row r="11" ht="15.75" customHeight="1"/>
     <row r="12" ht="15.75" customHeight="1"/>
     <row r="13" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/OO_Ingredient.xlsx
+++ b/JsonConverter/ExcelFiles/OO_Ingredient.xlsx
@@ -717,7 +717,7 @@
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>Stage2 보상으로 받는 달콤한 재료입니다.</t>
+          <t>Stage2 보상으로 받는 달콤한 재료입니다. 이후 요리와 거래 보상에 사용할 수 있습니다.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">

--- a/JsonConverter/ExcelFiles/OO_Ingredient.xlsx
+++ b/JsonConverter/ExcelFiles/OO_Ingredient.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
@@ -58,8 +58,16 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="?? ??"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -93,6 +101,11 @@
         <fgColor rgb="FFE2F0D9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -121,7 +134,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -140,6 +153,21 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -418,14 +446,14 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="14" customWidth="1" style="1" min="1" max="3"/>
     <col width="16" customWidth="1" style="1" min="4" max="4"/>
     <col width="14" customWidth="1" style="1" min="5" max="6"/>
-    <col width="12.54296875" customWidth="1" style="1" min="7" max="8"/>
-    <col width="12.54296875" customWidth="1" style="1" min="9" max="16384"/>
+    <col width="12.54296875" customWidth="1" style="1" min="7" max="9"/>
+    <col width="12.54296875" customWidth="1" style="1" min="10" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
@@ -525,33 +553,33 @@
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>Ing_Rice_01</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>쌀</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>춘향의 아버님이 내어주신 기름진 쌀. 모란의 기계 솥을 거치면 백성들의 허기를 단숨에 채워줄 따스한 밥과 떡이 된다.</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>춘향의 아버님이 내어주신 기름진 쌀. 절구에 찧으면 떡이 되고, 여러 요리의 기본 재료가 된다.</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
         <is>
           <t>Images/Food/Rice</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="13" t="inlineStr">
         <is>
           <t>일반</t>
         </is>
       </c>
-      <c r="F4" t="n">
-        <v>12</v>
+      <c r="F4" s="13" t="n">
+        <v>99</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
@@ -652,22 +680,13 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>??</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>???? ?? ??. ??? ??? ??? ??.</t>
-        </is>
-      </c>
+          <t>조기</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="n"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>Images/Food/Fish</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>??</t>
         </is>
       </c>
       <c r="F8" s="1" t="n">
@@ -705,37 +724,90 @@
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>Ing_Honey_01</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>꿀</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>Stage2 보상으로 받은 달콤한 꿀. 떡과 합치면 산군을 달랠 꿀떡을 만들 수 있다.</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>Images/Food/Honey</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="F10" s="14" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="11" ht="15.75" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Ing_KoreanCake_01</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>떡</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>Stage2 보상으로 받는 달콤한 재료입니다. 이후 요리와 거래 보상에 사용할 수 있습니다.</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Images/Food/Honey</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>Images/Food/KoreanCake</t>
+        </is>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="12" ht="15.75" customHeight="1">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>Ing_Carrot_01</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>당근</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>산군이 마음을 누그러뜨린 뒤 건네는 숲의 당근. 다음 여정의 보상 재료로 사용한다.</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>Images/Food/Carrot</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
         <is>
           <t>일반</t>
         </is>
       </c>
-      <c r="F10" s="1" t="n">
+      <c r="F12" s="13" t="n">
         <v>99</v>
       </c>
     </row>
-    <row r="11" ht="15.75" customHeight="1"/>
-    <row r="12" ht="15.75" customHeight="1"/>
     <row r="13" ht="15.75" customHeight="1"/>
     <row r="14" ht="15.75" customHeight="1"/>
     <row r="15" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/OO_Ingredient.xlsx
+++ b/JsonConverter/ExcelFiles/OO_Ingredient.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
@@ -66,8 +66,11 @@
       <name val="맑은 고딕"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -106,6 +109,21 @@
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2F0D9"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -134,7 +152,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -167,6 +185,18 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -449,104 +479,107 @@
   <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="14" customWidth="1" style="1" min="1" max="3"/>
-    <col width="16" customWidth="1" style="1" min="4" max="4"/>
-    <col width="14" customWidth="1" style="1" min="5" max="6"/>
+    <col width="20" customWidth="1" style="1" min="1" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" style="1" min="4" max="4"/>
+    <col width="12" customWidth="1" style="1" min="5" max="6"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
     <col width="12.54296875" customWidth="1" style="1" min="7" max="9"/>
     <col width="12.54296875" customWidth="1" style="1" min="10" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>재료 고유 ID</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>재료 이름</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="15" t="inlineStr">
         <is>
           <t>재료 설명</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="15" t="inlineStr">
         <is>
           <t>아이콘 리소스 경로</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="15" t="inlineStr">
         <is>
           <t>재료 등급</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="F1" s="16" t="inlineStr">
         <is>
           <t>최대 중첩 수</t>
         </is>
       </c>
     </row>
     <row r="2" ht="13" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="17" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="17" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" s="17" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="E2" s="17" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="17" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
     </row>
     <row r="3" ht="15.75" customFormat="1" customHeight="1" s="2">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>Id</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="18" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="18" t="inlineStr">
         <is>
           <t>IconPath</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="E3" s="18" t="inlineStr">
         <is>
           <t>Grade</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="F3" s="18" t="inlineStr">
         <is>
           <t>MaxStackCount</t>
         </is>
@@ -595,7 +628,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>?? ???? ?? ??? ??. ??? ? ?? ?? ??? ??? ???? ??.</t>
+          <t>첫 요리 튜토리얼에서 사용하는 기본 채소. 도마에 올려 손질하면 야채죽 재료가 됩니다.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -609,7 +642,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>12</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
@@ -791,7 +824,7 @@
       </c>
       <c r="C12" s="13" t="inlineStr">
         <is>
-          <t>산군이 마음을 누그러뜨린 뒤 건네는 숲의 당근. 다음 여정의 보상 재료로 사용한다.</t>
+          <t>산군이 약속의 뜻으로 건넨 숲의 당근. Stage4에서 당근전을 만들 때 사용합니다.</t>
         </is>
       </c>
       <c r="D12" s="13" t="inlineStr">

--- a/JsonConverter/ExcelFiles/OO_Ingredient.xlsx
+++ b/JsonConverter/ExcelFiles/OO_Ingredient.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="C4" s="13" t="inlineStr">
         <is>
-          <t>춘향의 아버님이 내어주신 기름진 쌀. 절구에 찧으면 떡이 되고, 여러 요리의 기본 재료가 된다.</t>
+          <t>춘양의 아버님이 내어주신 기름진 쌀입니다. 절구에 찧으면 떡이 되고, 야채죽과 여러 요리의 기본 재료가 되는 여정의 출발점입니다.</t>
         </is>
       </c>
       <c r="D4" s="13" t="inlineStr">
@@ -628,7 +628,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>첫 요리 튜토리얼에서 사용하는 기본 채소. 도마에 올려 손질하면 야채죽 재료가 됩니다.</t>
+          <t>첫 요리 튜토리얼에서 사용하는 기본 채소입니다. 도마에 올려 손질한 뒤 쌀과 함께 끓이면 동쪽 마을을 위한 야채죽이 됩니다.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -658,7 +658,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>나중에 호박죽과 다른 요리에 쓰일 달큰한 호박.</t>
+          <t>달큰한 맛을 내는 호박입니다. 쌀과 함께 끓이면 부드러운 호박죽이 되며, 푸드카리지의 따뜻한 요리 분위기를 보여 줍니다.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>청양고추</t>
+          <t>매운맛을 더하는 청양고추입니다. 김치찌개에 넣으면 강한 맛을 내며, 서쪽 도시의 답답한 분위기를 깨는 재료가 됩니다.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -716,7 +716,11 @@
           <t>조기</t>
         </is>
       </c>
-      <c r="C8" s="9" t="n"/>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>바다에서 얻은 조기입니다. 밥상 재료로 쓰이며, 육지와 숲을 넘어 더 넓은 여정으로 확장되는 느낌을 줍니다.</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>Images/Food/Fish</t>
@@ -739,7 +743,7 @@
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>Stage1 보상으로 받은 김치. 얼큰한 찌개를 만들 때 깊은 맛을 더합니다.</t>
+          <t>Stage1 보상으로 받은 김치입니다. 청양고추와 함께 끓이면 얼큰한 찌개가 되어 다음 스테이지의 진행에 힘을 보탭니다.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -769,7 +773,7 @@
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>Stage2 보상으로 받은 달콤한 꿀. 떡과 합치면 산군을 달랠 꿀떡을 만들 수 있다.</t>
+          <t>Stage2 보상으로 얻는 달콤한 꿀입니다. 떡과 조합하면 산군을 달랠 수 있는 꿀떡이 되어 Stage3 해결의 핵심이 됩니다.</t>
         </is>
       </c>
       <c r="D10" s="13" t="inlineStr">
@@ -799,7 +803,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>Stage2 보상으로 받는 달콤한 재료입니다. 이후 요리와 거래 보상에 사용할 수 있습니다.</t>
+          <t>보상으로 얻거나 절구로 만들 수 있는 떡 계열 재료입니다. 다른 재료와 조합되어 더 중요한 음식으로 이어지는 중간 재료입니다.</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
@@ -824,7 +828,7 @@
       </c>
       <c r="C12" s="13" t="inlineStr">
         <is>
-          <t>산군이 약속의 뜻으로 건넨 숲의 당근. Stage4에서 당근전을 만들 때 사용합니다.</t>
+          <t>산군이 약속의 뜻으로 건넨 숲의 당근입니다. 떡과 조합해 당근전분을 만들고, 다시 가마솥에 넣어 당근전을 완성합니다.</t>
         </is>
       </c>
       <c r="D12" s="13" t="inlineStr">
